--- a/03_Outputs/all/01_TablasDescriptivas/idx3_climatico.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx3_climatico.xlsx
@@ -399,7 +399,7 @@
         <v>-0.199774968</v>
       </c>
       <c r="D2">
-        <v>0.03624382213963218</v>
+        <v>0.03624382213963216</v>
       </c>
       <c r="E2">
         <v>-0.324996</v>
@@ -443,7 +443,7 @@
         <v>-0.09304</v>
       </c>
       <c r="D4">
-        <v>0.07304057643838534</v>
+        <v>0.07304057643838535</v>
       </c>
       <c r="E4">
         <v>-0.36</v>
